--- a/analyse_langue.xlsx
+++ b/analyse_langue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\doghm\Desktop\projet-infox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E619579-071D-4DE5-A790-478A64DAB3BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11A84C63-C16F-45A4-9445-1F7F499109CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
